--- a/bom/BT_Switch_Mechanical_BOM.xlsx
+++ b/bom/BT_Switch_Mechanical_BOM.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Land pattern shared with ESP32-S2-MINI-1 per Espressif; confirmed in KiCad footprint lib.</t>
+          <t>PCB uses the RF_Module:ESP32-S2-MINI-1 footprint, the land pattern shared with the S3 module. The schematic symbol is the S3 part.</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>VSON-10 (Package_SON:Texas_DRC0010J_ThermalVias)</t>
+          <t>VSON-10 (Package_SON:Texas_DRC0010J)</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
@@ -680,7 +680,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>U_CHG</t>
+          <t>U_CHG1</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SRN4018-2R2Y</t>
+          <t>SRN4018-2R2M</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>SMD 4x4mm</t>
+          <t>SMD 4x4mm (Inductor_SMD:L_Bourns-SRN4018)</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>0805 (may not fit 0603 at this voltage rating)</t>
+          <t>0603 (CL10A226MQ8NRNC, 6.3 V X5R)</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>REG1 output; confirm 0603 X5R 22uF/10V availability, else use 0805.</t>
+          <t>REG1 output; 0603 22 uF X5R. Expect heavy DC-bias derating at 3.3 V.</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>J_USB</t>
+          <t>J_USB1</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>J_BAT</t>
+          <t>J_BAT1</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>SW_RST</t>
+          <t>SW_RST1</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>SW_BOOT</t>
+          <t>SW_BOOT1</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>THT (Button_Switch_THT:SW_TH_Tactile_Omron_B3F-10xx)</t>
+          <t>THT (Button_Switch_THT:SW_TH_Tactile_Omron_B3F-100x)</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
@@ -1719,6 +1719,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>

--- a/bom/BT_Switch_Mechanical_BOM.xlsx
+++ b/bom/BT_Switch_Mechanical_BOM.xlsx
@@ -890,7 +890,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C4, C12</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -914,11 +914,11 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Charger VBUS input decoupling.</t>
+          <t>C4: charger VBUS input decoupling. C12: EN-to-GND, forms an RC reset delay with R5 (10 k x 1 uF).</t>
         </is>
       </c>
     </row>
